--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -8983,7 +8983,7 @@
       </c>
       <c r="F11" s="50" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G11" s="72" t="n">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>상시 가동 서버 가용성 확인 → 전개 방식 확정</t>
+          <t>상시 가동 서버 가용성 확인 → 전개 방식 확정 (클라우드 DMZ + 가상화 내부망)</t>
         </is>
       </c>
       <c r="D12" s="55" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="F12" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G12" s="72" t="n">

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F15" s="50" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G15" s="72" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F18" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G18" s="72" t="n">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="F19" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G19" s="72" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="F20" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G20" s="72" t="n">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="F21" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G21" s="72" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="F30" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G30" s="72" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F31" s="57" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G31" s="73" t="n">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="F32" s="57" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G32" s="73" t="n">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="F33" s="57" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G33" s="73" t="n">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="F48" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G48" s="72" t="n">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F49" s="57" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G49" s="73" t="n">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="F50" s="57" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G50" s="73" t="n">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F75" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G75" s="72" t="n">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="F76" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G76" s="72" t="n">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="F78" s="50" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G78" s="72" t="n">

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F34" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G34" s="171" t="n">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="F35" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G35" s="172" t="n">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="F36" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G36" s="172" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F37" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G37" s="172" t="n">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="F38" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G38" s="172" t="n">
@@ -11775,7 +11775,7 @@
       <c r="B39" s="138" t="n"/>
       <c r="C39" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 관리망 WireGuard VPN · 모바일 접속</t>
+          <t xml:space="preserve">    ▸ 관리망 VPN (Tailscale · WireGuard 기반) · 모바일 접속</t>
         </is>
       </c>
       <c r="D39" s="138" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F39" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G39" s="172" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F40" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G40" s="171" t="n">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="F41" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G41" s="172" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="F42" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G42" s="172" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="F43" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G43" s="172" t="n">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F44" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G44" s="172" t="n">

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1742,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="87" t="inlineStr">
         <is>
@@ -2218,6 +2219,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="87" t="inlineStr">
         <is>
@@ -2368,6 +2370,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="107" t="inlineStr">
         <is>
@@ -9974,7 +9977,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="85" t="inlineStr">
         <is>
-          <t>기간: 2026.09.02(수) ~ 10.16(금)  |  1인 프로젝트  |  2차 피드백 반영 개정 (2026.09.18) · 화면 설계 반영 (2026.09.19)  |  매 주차 종료 시점 시연 가능 상태 유지</t>
+          <t>기간: 2026.09.02(수) ~ 10.16(금)  |  1인 프로젝트  |  2차 피드백 반영 개정 (2026.09.18) · 화면 설계 반영 (2026.09.19) · 연구소장 피드백 반영 (2026.09.22)  |  매 주차 종료 시점 시연 가능 상태 유지</t>
         </is>
       </c>
     </row>
@@ -10954,10 +10957,10 @@
         </is>
       </c>
       <c r="G22" s="171" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="H22" s="171" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="I22" s="134">
         <f>IF(AND(G22&lt;&gt;"",H22&lt;&gt;""),H22-G22+1,"")</f>
@@ -11029,14 +11032,14 @@
       </c>
       <c r="F24" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G24" s="171" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H24" s="171" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I24" s="134">
         <f>IF(AND(G24&lt;&gt;"",H24&lt;&gt;""),H24-G24+1,"")</f>
@@ -11080,7 +11083,7 @@
       </c>
       <c r="F25" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G25" s="172" t="n">
@@ -11116,7 +11119,7 @@
       <c r="B26" s="138" t="n"/>
       <c r="C26" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 관문 방화벽 인스턴스 (포트 전달 · 차단 로그)</t>
+          <t xml:space="preserve">    ▸ 관문 방화벽 인스턴스 (포트 전달 · 차단 로그 · SSM 전용 엔드포인트 · DMZ 유출 전면 차단)</t>
         </is>
       </c>
       <c r="D26" s="138" t="inlineStr">
@@ -11131,14 +11134,14 @@
       </c>
       <c r="F26" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G26" s="172" t="n">
+        <v>46287</v>
+      </c>
+      <c r="H26" s="172" t="n">
         <v>46288</v>
-      </c>
-      <c r="H26" s="172" t="n">
-        <v>46290</v>
       </c>
       <c r="I26" s="138">
         <f>IF(AND(G26&lt;&gt;"",H26&lt;&gt;""),H26-G26+1,"")</f>
@@ -11167,7 +11170,7 @@
       <c r="B27" s="138" t="n"/>
       <c r="C27" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 허니팟 사설 서브넷 이전 및 로그 승계</t>
+          <t xml:space="preserve">    ▸ 허니팟 사설 서브넷 이전 (이미지 전 비밀 검사 · 로그 승계)</t>
         </is>
       </c>
       <c r="D27" s="138" t="inlineStr">
@@ -11186,10 +11189,10 @@
         </is>
       </c>
       <c r="G27" s="172" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="H27" s="172" t="n">
-        <v>46291</v>
+        <v>46289</v>
       </c>
       <c r="I27" s="138">
         <f>IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),H27-G27+1,"")</f>
@@ -11218,7 +11221,7 @@
       <c r="B28" s="138" t="n"/>
       <c r="C28" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ S3 단방향 반출 경로 · IAM 최소 권한</t>
+          <t xml:space="preserve">    ▸ 노드별 S3 쓰기 경계 · 관문 별도 역할 · DB 역할 최소 권한 (슈퍼유저 제거)</t>
         </is>
       </c>
       <c r="D28" s="138" t="inlineStr">
@@ -11233,14 +11236,14 @@
       </c>
       <c r="F28" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G28" s="172" t="n">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="H28" s="172" t="n">
-        <v>46292</v>
+        <v>46290</v>
       </c>
       <c r="I28" s="138">
         <f>IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),H28-G28+1,"")</f>
@@ -11248,7 +11251,7 @@
       </c>
       <c r="J28" s="139" t="inlineStr">
         <is>
-          <t>인프라 코드</t>
+          <t>인프라 코드 · DB 역할 정의</t>
         </is>
       </c>
       <c r="K28" s="137" t="inlineStr">
@@ -11288,10 +11291,10 @@
         </is>
       </c>
       <c r="G29" s="172" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="H29" s="172" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="I29" s="138">
         <f>IF(AND(G29&lt;&gt;"",H29&lt;&gt;""),H29-G29+1,"")</f>
@@ -11845,10 +11848,10 @@
         </is>
       </c>
       <c r="G40" s="171" t="n">
-        <v>46292</v>
+        <v>46286</v>
       </c>
       <c r="H40" s="171" t="n">
-        <v>46296</v>
+        <v>46288</v>
       </c>
       <c r="I40" s="134">
         <f>IF(AND(G40&lt;&gt;"",H40&lt;&gt;""),H40-G40+1,"")</f>
@@ -11896,10 +11899,10 @@
         </is>
       </c>
       <c r="G41" s="172" t="n">
-        <v>46292</v>
+        <v>46286</v>
       </c>
       <c r="H41" s="172" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="I41" s="138">
         <f>IF(AND(G41&lt;&gt;"",H41&lt;&gt;""),H41-G41+1,"")</f>
@@ -11994,10 +11997,10 @@
         </is>
       </c>
       <c r="G43" s="172" t="n">
-        <v>46295</v>
+        <v>46286</v>
       </c>
       <c r="H43" s="172" t="n">
-        <v>46296</v>
+        <v>46288</v>
       </c>
       <c r="I43" s="138">
         <f>IF(AND(G43&lt;&gt;"",H43&lt;&gt;""),H43-G43+1,"")</f>
@@ -12041,10 +12044,10 @@
         </is>
       </c>
       <c r="G44" s="172" t="n">
-        <v>46296</v>
+        <v>46286</v>
       </c>
       <c r="H44" s="172" t="n">
-        <v>46296</v>
+        <v>46288</v>
       </c>
       <c r="I44" s="138">
         <f>IF(AND(G44&lt;&gt;"",H44&lt;&gt;""),H44-G44+1,"")</f>
@@ -12092,10 +12095,10 @@
         </is>
       </c>
       <c r="G45" s="171" t="n">
-        <v>46291</v>
+        <v>46286</v>
       </c>
       <c r="H45" s="171" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="I45" s="134">
         <f>IF(AND(G45&lt;&gt;"",H45&lt;&gt;""),H45-G45+1,"")</f>
@@ -12139,14 +12142,14 @@
       </c>
       <c r="F46" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G46" s="172" t="n">
-        <v>46291</v>
+        <v>46286</v>
       </c>
       <c r="H46" s="172" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="I46" s="138">
         <f>IF(AND(G46&lt;&gt;"",H46&lt;&gt;""),H46-G46+1,"")</f>
@@ -12175,7 +12178,7 @@
       <c r="B47" s="138" t="n"/>
       <c r="C47" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 규칙 외부화 (DB 레코드 기반 관리)</t>
+          <t xml:space="preserve">    ▸ 공개 정보 연계 (자산 표 · KEV/CVE 원본 S3 · cve_probe 규칙 · 판정 기준 v3 · 사례 1건)</t>
         </is>
       </c>
       <c r="D47" s="138" t="inlineStr">
@@ -12194,10 +12197,10 @@
         </is>
       </c>
       <c r="G47" s="172" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="H47" s="172" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="I47" s="138">
         <f>IF(AND(G47&lt;&gt;"",H47&lt;&gt;""),H47-G47+1,"")</f>
@@ -12205,10 +12208,14 @@
       </c>
       <c r="J47" s="139" t="inlineStr">
         <is>
-          <t>소스코드</t>
-        </is>
-      </c>
-      <c r="K47" s="138" t="n"/>
+          <t>규칙 파일 · CVE 표 · 결과 문서</t>
+        </is>
+      </c>
+      <c r="K47" s="138" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="L47" s="138" t="n">
         <v>2</v>
       </c>
@@ -12222,7 +12229,7 @@
       <c r="B48" s="138" t="n"/>
       <c r="C48" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 압축 · 억제 규칙 정비</t>
+          <t xml:space="preserve">    ▸ Sigma→Loki PoC · 관문 Suricata 경보 · DNS 방화벽 (여유 시)</t>
         </is>
       </c>
       <c r="D48" s="138" t="inlineStr">
@@ -12241,10 +12248,10 @@
         </is>
       </c>
       <c r="G48" s="172" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="H48" s="172" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="I48" s="138">
         <f>IF(AND(G48&lt;&gt;"",H48&lt;&gt;""),H48-G48+1,"")</f>
@@ -12252,7 +12259,7 @@
       </c>
       <c r="J48" s="139" t="inlineStr">
         <is>
-          <t>소스코드</t>
+          <t>PoC 결과</t>
         </is>
       </c>
       <c r="K48" s="138" t="n"/>
@@ -12284,14 +12291,14 @@
       </c>
       <c r="F49" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G49" s="172" t="n">
-        <v>46296</v>
+        <v>46286</v>
       </c>
       <c r="H49" s="172" t="n">
-        <v>46297</v>
+        <v>46288</v>
       </c>
       <c r="I49" s="138">
         <f>IF(AND(G49&lt;&gt;"",H49&lt;&gt;""),H49-G49+1,"")</f>
@@ -12342,7 +12349,7 @@
         <v>46287</v>
       </c>
       <c r="H50" s="171" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="I50" s="134">
         <f>IF(AND(G50&lt;&gt;"",H50&lt;&gt;""),H50-G50+1,"")</f>
@@ -12386,14 +12393,14 @@
       </c>
       <c r="F51" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G51" s="172" t="n">
         <v>46287</v>
       </c>
       <c r="H51" s="172" t="n">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="I51" s="138">
         <f>IF(AND(G51&lt;&gt;"",H51&lt;&gt;""),H51-G51+1,"")</f>
@@ -12441,7 +12448,7 @@
         </is>
       </c>
       <c r="G52" s="172" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="H52" s="172" t="n">
         <v>46292</v>
@@ -12473,7 +12480,7 @@
       <c r="B53" s="138" t="n"/>
       <c r="C53" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 판정 화면 (제안 · 대조군 · 증거 고정 · 뒤집기 기록)</t>
+          <t xml:space="preserve">    ▸ 판정 화면 (제안 · 대조군 · 증거 고정 · 뒤집기 기록 · CVE · 자산 해당 · 성공 증거 칸)</t>
         </is>
       </c>
       <c r="D53" s="138" t="inlineStr">
@@ -12492,7 +12499,7 @@
         </is>
       </c>
       <c r="G53" s="172" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="H53" s="172" t="n">
         <v>46294</v>
@@ -12524,7 +12531,7 @@
       <c r="B54" s="138" t="n"/>
       <c r="C54" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 미판정 대시보드 · 심각도별 확인/판정 목표 시간 (모바일 대응)</t>
+          <t xml:space="preserve">    ▸ 미판정 대시보드 · 노드 상태 S-08 최소 · 판정 목표 시간 (모바일 대응)</t>
         </is>
       </c>
       <c r="D54" s="138" t="inlineStr">
@@ -12543,10 +12550,10 @@
         </is>
       </c>
       <c r="G54" s="172" t="n">
-        <v>46294</v>
+        <v>46298</v>
       </c>
       <c r="H54" s="172" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="I54" s="138">
         <f>IF(AND(G54&lt;&gt;"",H54&lt;&gt;""),H54-G54+1,"")</f>
@@ -12594,10 +12601,10 @@
         </is>
       </c>
       <c r="G55" s="172" t="n">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="H55" s="172" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="I55" s="138">
         <f>IF(AND(G55&lt;&gt;"",H55&lt;&gt;""),H55-G55+1,"")</f>
@@ -12641,10 +12648,10 @@
         </is>
       </c>
       <c r="G56" s="172" t="n">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="H56" s="172" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="I56" s="138">
         <f>IF(AND(G56&lt;&gt;"",H56&lt;&gt;""),H56-G56+1,"")</f>
@@ -12688,10 +12695,10 @@
         </is>
       </c>
       <c r="G57" s="172" t="n">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="H57" s="172" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="I57" s="138">
         <f>IF(AND(G57&lt;&gt;"",H57&lt;&gt;""),H57-G57+1,"")</f>
@@ -12716,7 +12723,7 @@
       <c r="B58" s="138" t="n"/>
       <c r="C58" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 감사 기록 · 계정 화면 (S-14 · S-15)</t>
+          <t xml:space="preserve">    ▸ 감사 기록 조회 (S-14 최소) · 계정 화면은 삭제 (CLI 유지)</t>
         </is>
       </c>
       <c r="D58" s="138" t="inlineStr">
@@ -12735,7 +12742,7 @@
         </is>
       </c>
       <c r="G58" s="172" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H58" s="172" t="n">
         <v>46302</v>
@@ -12763,7 +12770,7 @@
       <c r="B59" s="138" t="n"/>
       <c r="C59" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 연결 끊김 · 상태 화면 (S-10 · S-16)</t>
+          <t xml:space="preserve">    ▸ 연결 끊김 표시 (S-10 최소 · S-16 은 골격에 포함)</t>
         </is>
       </c>
       <c r="D59" s="138" t="inlineStr">
@@ -12782,10 +12789,10 @@
         </is>
       </c>
       <c r="G59" s="172" t="n">
-        <v>46302</v>
+        <v>46299</v>
       </c>
       <c r="H59" s="172" t="n">
-        <v>46303</v>
+        <v>46299</v>
       </c>
       <c r="I59" s="138">
         <f>IF(AND(G59&lt;&gt;"",H59&lt;&gt;""),H59-G59+1,"")</f>
@@ -12810,7 +12817,7 @@
       <c r="B60" s="138" t="n"/>
       <c r="C60" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 보고서 (회차 비교 · 주간 자동 생성, S-11)</t>
+          <t xml:space="preserve">    ▸ 비신뢰 로그 표시 시험 · CSP 검증 (콘솔 특정 방지, 보고서 화면은 삭제)</t>
         </is>
       </c>
       <c r="D60" s="138" t="inlineStr">
@@ -12829,10 +12836,10 @@
         </is>
       </c>
       <c r="G60" s="172" t="n">
-        <v>46303</v>
+        <v>46291</v>
       </c>
       <c r="H60" s="172" t="n">
-        <v>46304</v>
+        <v>46292</v>
       </c>
       <c r="I60" s="138">
         <f>IF(AND(G60&lt;&gt;"",H60&lt;&gt;""),H60-G60+1,"")</f>
@@ -12840,7 +12847,7 @@
       </c>
       <c r="J60" s="139" t="inlineStr">
         <is>
-          <t>소스코드</t>
+          <t>시험 코드 · 검증 기록</t>
         </is>
       </c>
       <c r="K60" s="138" t="n"/>
@@ -12880,10 +12887,10 @@
         </is>
       </c>
       <c r="G61" s="171" t="n">
-        <v>46295</v>
+        <v>46299</v>
       </c>
       <c r="H61" s="171" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="I61" s="134">
         <f>IF(AND(G61&lt;&gt;"",H61&lt;&gt;""),H61-G61+1,"")</f>
@@ -12935,7 +12942,7 @@
         </is>
       </c>
       <c r="G62" s="171" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H62" s="171" t="n">
         <v>46303</v>
@@ -12986,10 +12993,10 @@
         </is>
       </c>
       <c r="G63" s="172" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="H63" s="172" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="I63" s="138">
         <f>IF(AND(G63&lt;&gt;"",H63&lt;&gt;""),H63-G63+1,"")</f>
@@ -13037,7 +13044,7 @@
         </is>
       </c>
       <c r="G64" s="172" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="H64" s="172" t="n">
         <v>46301</v>
@@ -13088,7 +13095,7 @@
         </is>
       </c>
       <c r="G65" s="172" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H65" s="172" t="n">
         <v>46302</v>
@@ -13139,7 +13146,7 @@
         </is>
       </c>
       <c r="G66" s="172" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H66" s="172" t="n">
         <v>46303</v>
@@ -13175,7 +13182,7 @@
       </c>
       <c r="C67" s="135" t="inlineStr">
         <is>
-          <t>[A] 자동 차단 (fail2ban 연동 · 만료 · 감사 기록)</t>
+          <t>[A] 자동 차단 (fail2ban 최소 연동 · 만료 · 감사 기록 · 인프라 주소 차단 금지 목록)</t>
         </is>
       </c>
       <c r="D67" s="134" t="inlineStr">
@@ -13194,10 +13201,10 @@
         </is>
       </c>
       <c r="G67" s="171" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H67" s="171" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="I67" s="134">
         <f>IF(AND(G67&lt;&gt;"",H67&lt;&gt;""),H67-G67+1,"")</f>
@@ -13248,7 +13255,7 @@
         <v>46303</v>
       </c>
       <c r="H68" s="171" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="I68" s="134">
         <f>IF(AND(G68&lt;&gt;"",H68&lt;&gt;""),H68-G68+1,"")</f>
@@ -13292,14 +13299,14 @@
       </c>
       <c r="F69" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G69" s="171" t="n">
-        <v>46301</v>
+        <v>46286</v>
       </c>
       <c r="H69" s="171" t="n">
-        <v>46302</v>
+        <v>46287</v>
       </c>
       <c r="I69" s="134">
         <f>IF(AND(G69&lt;&gt;"",H69&lt;&gt;""),H69-G69+1,"")</f>
@@ -13407,7 +13414,7 @@
       </c>
       <c r="C72" s="135" t="inlineStr">
         <is>
-          <t>방화벽 규칙 검증 (DMZ→내부 차단 · 포트 확인)</t>
+          <t>방화벽 규칙 검증 · 격리 시험 (허니팟 장악 가정 · 9/25 1차 · 10/9 최종)</t>
         </is>
       </c>
       <c r="D72" s="134" t="inlineStr">
@@ -13426,7 +13433,7 @@
         </is>
       </c>
       <c r="G72" s="171" t="n">
-        <v>46303</v>
+        <v>46290</v>
       </c>
       <c r="H72" s="171" t="n">
         <v>46304</v>
@@ -13437,7 +13444,7 @@
       </c>
       <c r="J72" s="135" t="inlineStr">
         <is>
-          <t>검증 결과서</t>
+          <t>검증 결과서 · 격리 시험 결과</t>
         </is>
       </c>
       <c r="K72" s="137" t="inlineStr">
@@ -13481,7 +13488,7 @@
         </is>
       </c>
       <c r="G73" s="171" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="H73" s="171" t="n">
         <v>46305</v>
@@ -13539,7 +13546,7 @@
         <v>46304</v>
       </c>
       <c r="H74" s="171" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="I74" s="134">
         <f>IF(AND(G74&lt;&gt;"",H74&lt;&gt;""),H74-G74+1,"")</f>
@@ -13594,7 +13601,7 @@
         <v>46305</v>
       </c>
       <c r="H75" s="171" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="I75" s="134">
         <f>IF(AND(G75&lt;&gt;"",H75&lt;&gt;""),H75-G75+1,"")</f>
@@ -14007,7 +14014,7 @@
         </is>
       </c>
       <c r="G84" s="171" t="n">
-        <v>46268</v>
+        <v>46306</v>
       </c>
       <c r="H84" s="171" t="n">
         <v>46311</v>
@@ -14054,7 +14061,7 @@
         </is>
       </c>
       <c r="G85" s="171" t="n">
-        <v>46270</v>
+        <v>46306</v>
       </c>
       <c r="H85" s="171" t="n">
         <v>46311</v>
@@ -14195,7 +14202,7 @@
         </is>
       </c>
       <c r="G88" s="171" t="n">
-        <v>46290</v>
+        <v>46306</v>
       </c>
       <c r="H88" s="171" t="n">
         <v>46311</v>
@@ -15543,6 +15550,7 @@
       <c r="G22" s="63" t="n"/>
       <c r="H22" s="63" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="107" t="inlineStr">
         <is>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물 체크리스트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="WBS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="산출물 체크리스트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WBS'!$A$4:$L$106</definedName>
@@ -10953,14 +10953,14 @@
       </c>
       <c r="F22" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G22" s="171" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="H22" s="171" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="I22" s="134">
         <f>IF(AND(G22&lt;&gt;"",H22&lt;&gt;""),H22-G22+1,"")</f>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="F25" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G25" s="172" t="n">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="F26" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G26" s="172" t="n">
@@ -11185,14 +11185,14 @@
       </c>
       <c r="F27" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G27" s="172" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="H27" s="172" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="I27" s="138">
         <f>IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),H27-G27+1,"")</f>
@@ -11236,14 +11236,14 @@
       </c>
       <c r="F28" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G28" s="172" t="n">
         <v>46288</v>
       </c>
       <c r="H28" s="172" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="I28" s="138">
         <f>IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),H28-G28+1,"")</f>
@@ -11287,11 +11287,11 @@
       </c>
       <c r="F29" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G29" s="172" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="H29" s="172" t="n">
         <v>46294</v>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="F40" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G40" s="171" t="n">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="F41" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G41" s="172" t="n">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F43" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G43" s="172" t="n">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F44" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G44" s="172" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="F45" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G45" s="171" t="n">
@@ -12142,14 +12142,14 @@
       </c>
       <c r="F46" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G46" s="172" t="n">
         <v>46286</v>
       </c>
       <c r="H46" s="172" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="I46" s="138">
         <f>IF(AND(G46&lt;&gt;"",H46&lt;&gt;""),H46-G46+1,"")</f>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="F49" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G49" s="172" t="n">
@@ -12444,14 +12444,14 @@
       </c>
       <c r="F52" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G52" s="172" t="n">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="H52" s="172" t="n">
-        <v>46292</v>
+        <v>46288</v>
       </c>
       <c r="I52" s="138">
         <f>IF(AND(G52&lt;&gt;"",H52&lt;&gt;""),H52-G52+1,"")</f>
@@ -12495,14 +12495,14 @@
       </c>
       <c r="F53" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G53" s="172" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="H53" s="172" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="I53" s="138">
         <f>IF(AND(G53&lt;&gt;"",H53&lt;&gt;""),H53-G53+1,"")</f>
@@ -12546,14 +12546,14 @@
       </c>
       <c r="F54" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G54" s="172" t="n">
-        <v>46298</v>
+        <v>46288</v>
       </c>
       <c r="H54" s="172" t="n">
-        <v>46298</v>
+        <v>46288</v>
       </c>
       <c r="I54" s="138">
         <f>IF(AND(G54&lt;&gt;"",H54&lt;&gt;""),H54-G54+1,"")</f>
@@ -12597,14 +12597,14 @@
       </c>
       <c r="F55" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G55" s="172" t="n">
-        <v>46299</v>
+        <v>46288</v>
       </c>
       <c r="H55" s="172" t="n">
-        <v>46299</v>
+        <v>46288</v>
       </c>
       <c r="I55" s="138">
         <f>IF(AND(G55&lt;&gt;"",H55&lt;&gt;""),H55-G55+1,"")</f>
@@ -12644,14 +12644,14 @@
       </c>
       <c r="F56" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G56" s="172" t="n">
-        <v>46302</v>
+        <v>46288</v>
       </c>
       <c r="H56" s="172" t="n">
-        <v>46302</v>
+        <v>46288</v>
       </c>
       <c r="I56" s="138">
         <f>IF(AND(G56&lt;&gt;"",H56&lt;&gt;""),H56-G56+1,"")</f>
@@ -12691,14 +12691,14 @@
       </c>
       <c r="F57" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G57" s="172" t="n">
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="H57" s="172" t="n">
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="I57" s="138">
         <f>IF(AND(G57&lt;&gt;"",H57&lt;&gt;""),H57-G57+1,"")</f>
@@ -12738,14 +12738,14 @@
       </c>
       <c r="F58" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G58" s="172" t="n">
-        <v>46302</v>
+        <v>46288</v>
       </c>
       <c r="H58" s="172" t="n">
-        <v>46302</v>
+        <v>46288</v>
       </c>
       <c r="I58" s="138">
         <f>IF(AND(G58&lt;&gt;"",H58&lt;&gt;""),H58-G58+1,"")</f>
@@ -12785,14 +12785,14 @@
       </c>
       <c r="F59" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G59" s="172" t="n">
-        <v>46299</v>
+        <v>46288</v>
       </c>
       <c r="H59" s="172" t="n">
-        <v>46299</v>
+        <v>46288</v>
       </c>
       <c r="I59" s="138">
         <f>IF(AND(G59&lt;&gt;"",H59&lt;&gt;""),H59-G59+1,"")</f>
@@ -12938,11 +12938,11 @@
       </c>
       <c r="F62" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G62" s="171" t="n">
-        <v>46300</v>
+        <v>46289</v>
       </c>
       <c r="H62" s="171" t="n">
         <v>46303</v>
@@ -12989,14 +12989,14 @@
       </c>
       <c r="F63" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G63" s="172" t="n">
-        <v>46300</v>
+        <v>46289</v>
       </c>
       <c r="H63" s="172" t="n">
-        <v>46300</v>
+        <v>46290</v>
       </c>
       <c r="I63" s="138">
         <f>IF(AND(G63&lt;&gt;"",H63&lt;&gt;""),H63-G63+1,"")</f>
@@ -13091,14 +13091,14 @@
       </c>
       <c r="F65" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G65" s="172" t="n">
-        <v>46302</v>
+        <v>46289</v>
       </c>
       <c r="H65" s="172" t="n">
-        <v>46302</v>
+        <v>46290</v>
       </c>
       <c r="I65" s="138">
         <f>IF(AND(G65&lt;&gt;"",H65&lt;&gt;""),H65-G65+1,"")</f>
@@ -13142,14 +13142,14 @@
       </c>
       <c r="F66" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G66" s="172" t="n">
-        <v>46303</v>
+        <v>46289</v>
       </c>
       <c r="H66" s="172" t="n">
-        <v>46303</v>
+        <v>46290</v>
       </c>
       <c r="I66" s="138">
         <f>IF(AND(G66&lt;&gt;"",H66&lt;&gt;""),H66-G66+1,"")</f>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="F72" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="G72" s="171" t="n">

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A2:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1742,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="87" t="inlineStr">
         <is>
@@ -2219,7 +2218,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="87" t="inlineStr">
         <is>
@@ -2370,7 +2368,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="107" t="inlineStr">
         <is>
@@ -12178,7 +12175,7 @@
       <c r="B47" s="138" t="n"/>
       <c r="C47" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 공개 정보 연계 (자산 표 · KEV/CVE 원본 S3 · cve_probe 규칙 · 판정 기준 v3 · 사례 1건)</t>
+          <t xml:space="preserve">    ▸ 공개 정보 연계 (자산 표 · KEV/CVE 원본 S3 · 서명 규칙 c1 · 판정 기준 §8 · 사례 2건 · 주목 CVE)</t>
         </is>
       </c>
       <c r="D47" s="138" t="inlineStr">
@@ -12193,14 +12190,14 @@
       </c>
       <c r="F47" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G47" s="172" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="H47" s="172" t="n">
-        <v>46297</v>
+        <v>46290</v>
       </c>
       <c r="I47" s="138">
         <f>IF(AND(G47&lt;&gt;"",H47&lt;&gt;""),H47-G47+1,"")</f>
@@ -12342,14 +12339,14 @@
       </c>
       <c r="F50" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G50" s="171" t="n">
         <v>46287</v>
       </c>
       <c r="H50" s="171" t="n">
-        <v>46303</v>
+        <v>46290</v>
       </c>
       <c r="I50" s="134">
         <f>IF(AND(G50&lt;&gt;"",H50&lt;&gt;""),H50-G50+1,"")</f>
@@ -12817,7 +12814,7 @@
       <c r="B60" s="138" t="n"/>
       <c r="C60" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 비신뢰 로그 표시 시험 · CSP 검증 (콘솔 특정 방지, 보고서 화면은 삭제)</t>
+          <t xml:space="preserve">    ▸ 비신뢰 로그 표시 시험 · CSP 검증 (숨은 문자 표식 · 긴 값 접기 · 콘솔 특정 방지 · 통계 페이지 내부화 · 알림 값 정리, 보고서 화면은 삭제)</t>
         </is>
       </c>
       <c r="D60" s="138" t="inlineStr">
@@ -12832,14 +12829,14 @@
       </c>
       <c r="F60" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G60" s="172" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="H60" s="172" t="n">
-        <v>46292</v>
+        <v>46290</v>
       </c>
       <c r="I60" s="138">
         <f>IF(AND(G60&lt;&gt;"",H60&lt;&gt;""),H60-G60+1,"")</f>
@@ -15550,7 +15547,6 @@
       <c r="G22" s="63" t="n"/>
       <c r="H22" s="63" t="n"/>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="107" t="inlineStr">
         <is>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -13521,7 +13521,7 @@
       </c>
       <c r="C74" s="135" t="inlineStr">
         <is>
-          <t>장애 주입 시험 (콘솔 강제 종료 · 전환 시간 측정)</t>
+          <t>장애 주입 시험 (콘솔 강제 종료 · VM 강제 끔 · 전환 시간 측정 · HAProxy 보강 전후 21회)</t>
         </is>
       </c>
       <c r="D74" s="134" t="inlineStr">
@@ -13536,14 +13536,14 @@
       </c>
       <c r="F74" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G74" s="171" t="n">
-        <v>46304</v>
+        <v>46290</v>
       </c>
       <c r="H74" s="171" t="n">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="I74" s="134">
         <f>IF(AND(G74&lt;&gt;"",H74&lt;&gt;""),H74-G74+1,"")</f>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -13576,7 +13576,7 @@
       </c>
       <c r="C75" s="135" t="inlineStr">
         <is>
-          <t>백업 복원 훈련 (RTO 실측)</t>
+          <t>백업 복원 훈련 (새 서버 복원 · 역할 목록 · 무결성 · 원장 재적재 대조 · RTO 5분 53초 · 복원 런북)</t>
         </is>
       </c>
       <c r="D75" s="134" t="inlineStr">
@@ -13591,14 +13591,14 @@
       </c>
       <c r="F75" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G75" s="171" t="n">
-        <v>46305</v>
+        <v>46292</v>
       </c>
       <c r="H75" s="171" t="n">
-        <v>46305</v>
+        <v>46292</v>
       </c>
       <c r="I75" s="134">
         <f>IF(AND(G75&lt;&gt;"",H75&lt;&gt;""),H75-G75+1,"")</f>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -13179,7 +13179,7 @@
       </c>
       <c r="C67" s="135" t="inlineStr">
         <is>
-          <t>[A] 자동 차단 (fail2ban 최소 연동 · 만료 · 감사 기록 · 인프라 주소 차단 금지 목록)</t>
+          <t>[A] 차단 자동 집행 (관문 fail2ban 연동 · 만료 · 감사 기록 · 인프라 주소 차단 금지 목록)</t>
         </is>
       </c>
       <c r="D67" s="134" t="inlineStr">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="F67" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G67" s="171" t="n">
-        <v>46301</v>
+        <v>46292</v>
       </c>
       <c r="H67" s="171" t="n">
-        <v>46301</v>
+        <v>46292</v>
       </c>
       <c r="I67" s="134">
         <f>IF(AND(G67&lt;&gt;"",H67&lt;&gt;""),H67-G67+1,"")</f>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WBS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="산출물 체크리스트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대시보드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물 체크리스트" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WBS'!$A$4:$L$106</definedName>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="C61" s="135" t="inlineStr">
         <is>
-          <t>[D] 정상 트래픽 정의 및 생성 (오탐 측정 기준)</t>
+          <t>[D] 정상 트래픽 정의 및 생성 (오탐 측정 기준 · 실험 DB 사본 · 시나리오 16개)</t>
         </is>
       </c>
       <c r="D61" s="134" t="inlineStr">
@@ -12880,14 +12880,14 @@
       </c>
       <c r="F61" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G61" s="171" t="n">
-        <v>46299</v>
+        <v>46293</v>
       </c>
       <c r="H61" s="171" t="n">
-        <v>46300</v>
+        <v>46293</v>
       </c>
       <c r="I61" s="134">
         <f>IF(AND(G61&lt;&gt;"",H61&lt;&gt;""),H61-G61+1,"")</f>
@@ -13022,7 +13022,7 @@
       <c r="B64" s="138" t="n"/>
       <c r="C64" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 디코이 규칙 후보 → 콘솔 로그 리플레이</t>
+          <t xml:space="preserve">    ▸ 디코이 규칙 후보 → 콘솔 로그 리플레이 (w2 · 임계치 후보 3 · 8 · 오탐 ↔ 재현율 결과표)</t>
         </is>
       </c>
       <c r="D64" s="138" t="inlineStr">
@@ -13037,14 +13037,14 @@
       </c>
       <c r="F64" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G64" s="172" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="H64" s="172" t="n">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="I64" s="138">
         <f>IF(AND(G64&lt;&gt;"",H64&lt;&gt;""),H64-G64+1,"")</f>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -13245,14 +13245,14 @@
       </c>
       <c r="F68" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G68" s="171" t="n">
-        <v>46303</v>
+        <v>46293</v>
       </c>
       <c r="H68" s="171" t="n">
-        <v>46303</v>
+        <v>46293</v>
       </c>
       <c r="I68" s="134">
         <f>IF(AND(G68&lt;&gt;"",H68&lt;&gt;""),H68-G68+1,"")</f>

--- a/docs/OpsLoop_WBS_v2.0.xlsx
+++ b/docs/OpsLoop_WBS_v2.0.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1742,6 +1742,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="87" t="inlineStr">
         <is>
@@ -2218,6 +2219,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="87" t="inlineStr">
         <is>
@@ -2368,6 +2370,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="107" t="inlineStr">
         <is>
@@ -12088,14 +12091,14 @@
       </c>
       <c r="F45" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G45" s="171" t="n">
         <v>46286</v>
       </c>
       <c r="H45" s="171" t="n">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="I45" s="134">
         <f>IF(AND(G45&lt;&gt;"",H45&lt;&gt;""),H45-G45+1,"")</f>
@@ -12226,7 +12229,7 @@
       <c r="B48" s="138" t="n"/>
       <c r="C48" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ Sigma→Loki PoC · 관문 Suricata 경보 · DNS 방화벽 (여유 시)</t>
+          <t xml:space="preserve">      ▸ Sigma 공개 웹 규칙 변환 PoC (c1 서명 형식 · R107 · 리플레이 비교, Suricata · DNS 방화벽은 제외)</t>
         </is>
       </c>
       <c r="D48" s="138" t="inlineStr">
@@ -12241,14 +12244,14 @@
       </c>
       <c r="F48" s="134" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G48" s="172" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="H48" s="172" t="n">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="I48" s="138">
         <f>IF(AND(G48&lt;&gt;"",H48&lt;&gt;""),H48-G48+1,"")</f>
@@ -12346,7 +12349,7 @@
         <v>46287</v>
       </c>
       <c r="H50" s="171" t="n">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="I50" s="134">
         <f>IF(AND(G50&lt;&gt;"",H50&lt;&gt;""),H50-G50+1,"")</f>
@@ -12426,7 +12429,7 @@
       <c r="B52" s="138" t="n"/>
       <c r="C52" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 인시던트 목록 · 상세 (증거 집약 · 담당 표시)</t>
+          <t xml:space="preserve">    ▸ 인시던트 목록 · 상세 (증거 집약 · 담당 표시) · 출발지 분석 · 도구 지문 묶음 (S-09)</t>
         </is>
       </c>
       <c r="D52" s="138" t="inlineStr">
@@ -12448,7 +12451,7 @@
         <v>46288</v>
       </c>
       <c r="H52" s="172" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="I52" s="138">
         <f>IF(AND(G52&lt;&gt;"",H52&lt;&gt;""),H52-G52+1,"")</f>
@@ -12528,7 +12531,7 @@
       <c r="B54" s="138" t="n"/>
       <c r="C54" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 미판정 대시보드 · 노드 상태 S-08 최소 · 판정 목표 시간 (모바일 대응)</t>
+          <t xml:space="preserve">    ▸ 미판정 대시보드 · 노드 상태 S-08 최소 · 판정 목표 시간 (모바일 대응) · 관제 대상 상태판 · CVE 배지 · 등록 노드 카드</t>
         </is>
       </c>
       <c r="D54" s="138" t="inlineStr">
@@ -12550,7 +12553,7 @@
         <v>46288</v>
       </c>
       <c r="H54" s="172" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="I54" s="138">
         <f>IF(AND(G54&lt;&gt;"",H54&lt;&gt;""),H54-G54+1,"")</f>
@@ -12720,7 +12723,7 @@
       <c r="B58" s="138" t="n"/>
       <c r="C58" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 감사 기록 조회 (S-14 최소) · 계정 화면은 삭제 (CLI 유지)</t>
+          <t xml:space="preserve">      ▸ 감사 기록 조회 (S-14) · 계정 관리 (역할 변경 · 비활성 · 관제사 · 조회자 추가 · 삭제 · 비밀번호, 관리자는 CLI)</t>
         </is>
       </c>
       <c r="D58" s="138" t="inlineStr">
@@ -12742,7 +12745,7 @@
         <v>46288</v>
       </c>
       <c r="H58" s="172" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="I58" s="138">
         <f>IF(AND(G58&lt;&gt;"",H58&lt;&gt;""),H58-G58+1,"")</f>
@@ -12814,7 +12817,7 @@
       <c r="B60" s="138" t="n"/>
       <c r="C60" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ▸ 비신뢰 로그 표시 시험 · CSP 검증 (숨은 문자 표식 · 긴 값 접기 · 콘솔 특정 방지 · 통계 페이지 내부화 · 알림 값 정리, 보고서 화면은 삭제)</t>
+          <t xml:space="preserve">    ▸ 비신뢰 로그 표시 시험 · CSP 검증 (숨은 문자 표식 · 긴 값 접기 · 콘솔 특정 방지 · 통계 페이지 내부화 · 알림 값 정리) · 기간 보고서 인쇄 (S-11) · 화면 문구 정리 · 잘못된 입력 422</t>
         </is>
       </c>
       <c r="D60" s="138" t="inlineStr">
@@ -12836,7 +12839,7 @@
         <v>46290</v>
       </c>
       <c r="H60" s="172" t="n">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="I60" s="138">
         <f>IF(AND(G60&lt;&gt;"",H60&lt;&gt;""),H60-G60+1,"")</f>
@@ -12935,14 +12938,14 @@
       </c>
       <c r="F62" s="134" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G62" s="171" t="n">
         <v>46289</v>
       </c>
       <c r="H62" s="171" t="n">
-        <v>46303</v>
+        <v>46293</v>
       </c>
       <c r="I62" s="134">
         <f>IF(AND(G62&lt;&gt;"",H62&lt;&gt;""),H62-G62+1,"")</f>
@@ -13179,7 +13182,7 @@
       </c>
       <c r="C67" s="135" t="inlineStr">
         <is>
-          <t>[A] 차단 자동 집행 (관문 fail2ban 연동 · 만료 · 감사 기록 · 인프라 주소 차단 금지 목록)</t>
+          <t>[A] 차단 자동 집행 (관문 fail2ban 연동 · 만료 · 감사 기록 · 인프라 주소 차단 금지 목록) · 내부 방화벽 집행 · 집행 지점별 결과</t>
         </is>
       </c>
       <c r="D67" s="134" t="inlineStr">
@@ -13201,7 +13204,7 @@
         <v>46292</v>
       </c>
       <c r="H67" s="171" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="I67" s="134">
         <f>IF(AND(G67&lt;&gt;"",H67&lt;&gt;""),H67-G67+1,"")</f>
@@ -13521,7 +13524,7 @@
       </c>
       <c r="C74" s="135" t="inlineStr">
         <is>
-          <t>장애 주입 시험 (콘솔 강제 종료 · VM 강제 끔 · 전환 시간 측정 · HAProxy 보강 전후 21회)</t>
+          <t>장애 주입 시험 (콘솔 강제 종료 · VM 강제 끔 · 전환 시간 측정 · HAProxy 보강 전후 21회 · 이중화 후속 반영 뒤 재측정)</t>
         </is>
       </c>
       <c r="D74" s="134" t="inlineStr">
@@ -13543,7 +13546,7 @@
         <v>46290</v>
       </c>
       <c r="H74" s="171" t="n">
-        <v>46291</v>
+        <v>46294</v>
       </c>
       <c r="I74" s="134">
         <f>IF(AND(G74&lt;&gt;"",H74&lt;&gt;""),H74-G74+1,"")</f>
@@ -15547,6 +15550,7 @@
       <c r="G22" s="63" t="n"/>
       <c r="H22" s="63" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="107" t="inlineStr">
         <is>
